--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28.3464535166944</v>
+        <v>19.84251746168608</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22.52630773887482</v>
+        <v>15.76841541721237</v>
       </c>
     </row>
     <row r="9">
@@ -784,7 +784,7 @@
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>28.48831187502621</v>
+        <v>19.94181831251835</v>
       </c>
       <c r="F11" t="n">
-        <v>22.52630773887482</v>
+        <v>15.76841541721237</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>22.52630773887482</v>
+        <v>15.76841541721237</v>
       </c>
     </row>
     <row r="13">
@@ -1054,10 +1054,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.43678064165957</v>
+        <v>16.4057464491617</v>
       </c>
       <c r="C2" t="n">
-        <v>25.89161707917699</v>
+        <v>18.12413195542389</v>
       </c>
       <c r="D2" t="n">
-        <v>28.3464535166944</v>
+        <v>19.84251746168608</v>
       </c>
       <c r="E2" t="n">
-        <v>30.80128995421182</v>
+        <v>21.56090296794827</v>
       </c>
       <c r="F2" t="n">
-        <v>33.25612639172922</v>
+        <v>23.27928847421045</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23.43678064165957</v>
+        <v>16.4057464491617</v>
       </c>
       <c r="C3" t="n">
-        <v>25.89161707917699</v>
+        <v>18.12413195542389</v>
       </c>
       <c r="D3" t="n">
-        <v>28.3464535166944</v>
+        <v>19.84251746168608</v>
       </c>
       <c r="E3" t="n">
-        <v>30.80128995421182</v>
+        <v>21.56090296794827</v>
       </c>
       <c r="F3" t="n">
-        <v>33.25612639172922</v>
+        <v>23.27928847421045</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.43678064165957</v>
+        <v>16.4057464491617</v>
       </c>
       <c r="C4" t="n">
-        <v>25.89161707917699</v>
+        <v>18.12413195542389</v>
       </c>
       <c r="D4" t="n">
-        <v>28.3464535166944</v>
+        <v>19.84251746168608</v>
       </c>
       <c r="E4" t="n">
-        <v>30.80128995421182</v>
+        <v>21.56090296794827</v>
       </c>
       <c r="F4" t="n">
-        <v>33.25612639172922</v>
+        <v>23.27928847421045</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.43678064165957</v>
+        <v>16.4057464491617</v>
       </c>
       <c r="C5" t="n">
-        <v>25.89161707917699</v>
+        <v>18.12413195542389</v>
       </c>
       <c r="D5" t="n">
-        <v>28.3464535166944</v>
+        <v>19.84251746168608</v>
       </c>
       <c r="E5" t="n">
-        <v>30.80128995421182</v>
+        <v>21.56090296794827</v>
       </c>
       <c r="F5" t="n">
-        <v>33.25612639172922</v>
+        <v>23.27928847421045</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23.43678064165957</v>
+        <v>16.4057464491617</v>
       </c>
       <c r="C6" t="n">
-        <v>25.89161707917699</v>
+        <v>18.12413195542389</v>
       </c>
       <c r="D6" t="n">
-        <v>28.3464535166944</v>
+        <v>19.84251746168608</v>
       </c>
       <c r="E6" t="n">
-        <v>30.80128995421182</v>
+        <v>21.56090296794827</v>
       </c>
       <c r="F6" t="n">
-        <v>33.25612639172922</v>
+        <v>23.27928847421045</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>30.17</v>
+        <v>21.67</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>30.51</v>
+        <v>22.01</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>30.63</v>
+        <v>22.12</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.25</v>
+        <v>17.24</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.24</v>
+        <v>17.39</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.222412374522251e-25</v>
+        <v>4.222412374522252e-25</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.39</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.222412374522252e-25</v>
+        <v>4.222412374522251e-25</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.222412374522252e-25</v>
+        <v>4.222412374522251e-25</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.84251746168608</v>
+        <v>19.99754651966026</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.22655070190745</v>
+        <v>32.48508799610302</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15.76841541721237</v>
+        <v>15.8845239032425</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.210275160339314</v>
+        <v>1.212107678294606</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.222412374522251e-25</v>
+        <v>4.216398688435863e-25</v>
       </c>
     </row>
     <row r="16">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>135.1962514606568</v>
+        <v>140.2937784535326</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>306.0492587910131</v>
+        <v>307.2032856013886</v>
       </c>
     </row>
     <row r="5">
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>779.2532069040534</v>
+        <v>785.5047607073052</v>
       </c>
     </row>
     <row r="12">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32.22655070190745</v>
+        <v>32.48508799610302</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32.22655070190745</v>
+        <v>32.48508799610302</v>
       </c>
     </row>
     <row r="15">
@@ -784,7 +784,7 @@
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>19.94181831251835</v>
+        <v>20.08865705767386</v>
       </c>
       <c r="F11" t="n">
-        <v>15.76841541721237</v>
+        <v>15.8845239032425</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>15.76841541721237</v>
+        <v>15.8845239032425</v>
       </c>
     </row>
     <row r="13">
@@ -1054,11 +1054,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.4057464491617</v>
+        <v>16.52976969554105</v>
       </c>
       <c r="C2" t="n">
-        <v>18.12413195542389</v>
+        <v>18.26365810760066</v>
       </c>
       <c r="D2" t="n">
-        <v>19.84251746168608</v>
+        <v>19.99754651966026</v>
       </c>
       <c r="E2" t="n">
-        <v>21.56090296794827</v>
+        <v>21.73143493171987</v>
       </c>
       <c r="F2" t="n">
-        <v>23.27928847421045</v>
+        <v>23.46532334377947</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.4057464491617</v>
+        <v>16.52976969554105</v>
       </c>
       <c r="C3" t="n">
-        <v>18.12413195542389</v>
+        <v>18.26365810760066</v>
       </c>
       <c r="D3" t="n">
-        <v>19.84251746168608</v>
+        <v>19.99754651966026</v>
       </c>
       <c r="E3" t="n">
-        <v>21.56090296794827</v>
+        <v>21.73143493171987</v>
       </c>
       <c r="F3" t="n">
-        <v>23.27928847421045</v>
+        <v>23.46532334377947</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.4057464491617</v>
+        <v>16.52976969554105</v>
       </c>
       <c r="C4" t="n">
-        <v>18.12413195542389</v>
+        <v>18.26365810760066</v>
       </c>
       <c r="D4" t="n">
-        <v>19.84251746168608</v>
+        <v>19.99754651966026</v>
       </c>
       <c r="E4" t="n">
-        <v>21.56090296794827</v>
+        <v>21.73143493171987</v>
       </c>
       <c r="F4" t="n">
-        <v>23.27928847421045</v>
+        <v>23.46532334377947</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16.4057464491617</v>
+        <v>16.52976969554105</v>
       </c>
       <c r="C5" t="n">
-        <v>18.12413195542389</v>
+        <v>18.26365810760066</v>
       </c>
       <c r="D5" t="n">
-        <v>19.84251746168608</v>
+        <v>19.99754651966026</v>
       </c>
       <c r="E5" t="n">
-        <v>21.56090296794827</v>
+        <v>21.73143493171987</v>
       </c>
       <c r="F5" t="n">
-        <v>23.27928847421045</v>
+        <v>23.46532334377947</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.4057464491617</v>
+        <v>16.52976969554105</v>
       </c>
       <c r="C6" t="n">
-        <v>18.12413195542389</v>
+        <v>18.26365810760066</v>
       </c>
       <c r="D6" t="n">
-        <v>19.84251746168608</v>
+        <v>19.99754651966026</v>
       </c>
       <c r="E6" t="n">
-        <v>21.56090296794827</v>
+        <v>21.73143493171987</v>
       </c>
       <c r="F6" t="n">
-        <v>23.27928847421045</v>
+        <v>23.46532334377947</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>21.67</v>
+        <v>21.82</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>22.01</v>
+        <v>22.17</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>22.12</v>
+        <v>22.28</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.6</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.99754651966026</v>
+        <v>21.11997651409043</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15.8845239032425</v>
+        <v>18.6905988893179</v>
       </c>
     </row>
     <row r="9">
@@ -784,7 +784,7 @@
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>20.08865705767386</v>
+        <v>23.63741170822269</v>
       </c>
       <c r="F11" t="n">
-        <v>15.8845239032425</v>
+        <v>18.6905988893179</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>15.8845239032425</v>
+        <v>18.6905988893179</v>
       </c>
     </row>
     <row r="13">
@@ -1054,10 +1054,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.52976969554105</v>
+        <v>16.68744859394529</v>
       </c>
       <c r="C2" t="n">
-        <v>18.26365810760066</v>
+        <v>18.39415660140149</v>
       </c>
       <c r="D2" t="n">
-        <v>19.99754651966026</v>
+        <v>20.10086460885771</v>
       </c>
       <c r="E2" t="n">
-        <v>21.73143493171987</v>
+        <v>21.80757261631391</v>
       </c>
       <c r="F2" t="n">
-        <v>23.46532334377947</v>
+        <v>23.5142806237701</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.52976969554105</v>
+        <v>17.19700454656165</v>
       </c>
       <c r="C3" t="n">
-        <v>18.26365810760066</v>
+        <v>18.90371255401786</v>
       </c>
       <c r="D3" t="n">
-        <v>19.99754651966026</v>
+        <v>20.61042056147406</v>
       </c>
       <c r="E3" t="n">
-        <v>21.73143493171987</v>
+        <v>22.31712856893027</v>
       </c>
       <c r="F3" t="n">
-        <v>23.46532334377947</v>
+        <v>24.02383657638646</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.52976969554105</v>
+        <v>17.70656049917802</v>
       </c>
       <c r="C4" t="n">
-        <v>18.26365810760066</v>
+        <v>19.41326850663422</v>
       </c>
       <c r="D4" t="n">
-        <v>19.99754651966026</v>
+        <v>21.11997651409043</v>
       </c>
       <c r="E4" t="n">
-        <v>21.73143493171987</v>
+        <v>22.82668452154663</v>
       </c>
       <c r="F4" t="n">
-        <v>23.46532334377947</v>
+        <v>24.53339252900282</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16.52976969554105</v>
+        <v>18.21611645179438</v>
       </c>
       <c r="C5" t="n">
-        <v>18.26365810760066</v>
+        <v>19.92282445925058</v>
       </c>
       <c r="D5" t="n">
-        <v>19.99754651966026</v>
+        <v>21.62953246670679</v>
       </c>
       <c r="E5" t="n">
-        <v>21.73143493171987</v>
+        <v>23.33624047416299</v>
       </c>
       <c r="F5" t="n">
-        <v>23.46532334377947</v>
+        <v>25.04294848161918</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.52976969554105</v>
+        <v>18.72567240441074</v>
       </c>
       <c r="C6" t="n">
-        <v>18.26365810760066</v>
+        <v>20.43238041186695</v>
       </c>
       <c r="D6" t="n">
-        <v>19.99754651966026</v>
+        <v>22.13908841932315</v>
       </c>
       <c r="E6" t="n">
-        <v>21.73143493171987</v>
+        <v>23.84579642677936</v>
       </c>
       <c r="F6" t="n">
-        <v>23.46532334377947</v>
+        <v>25.55250443423555</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>21.82</v>
+        <v>21.83</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>22.17</v>
+        <v>21.96</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>22.28</v>
+        <v>22.01</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.9</v>
+        <v>17.47</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.11997651409043</v>
+        <v>20.43098553053134</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.48508799610302</v>
+        <v>31.33045183475965</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18.6905988893179</v>
+        <v>18.18048939983071</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.212107678294606</v>
+        <v>1.214902242349383</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.216398688435863e-25</v>
+        <v>2713.443597791534</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.97215226305253e-29</v>
+        <v>0.1283629848710788</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>237.7776966523835</v>
+        <v>215.191058659085</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>140.2937784535326</v>
+        <v>140.0046718952724</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>307.2032856013886</v>
+        <v>302.159382783397</v>
       </c>
     </row>
     <row r="5">
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>785.5047607073052</v>
+        <v>757.5851133377544</v>
       </c>
     </row>
     <row r="12">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32.48508799610302</v>
+        <v>31.33045183475965</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32.48508799610302</v>
+        <v>31.33045183475965</v>
       </c>
     </row>
     <row r="15">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>23.63741170822269</v>
+        <v>22.99229230404076</v>
       </c>
       <c r="F11" t="n">
-        <v>18.6905988893179</v>
+        <v>18.18048939983071</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>18.6905988893179</v>
+        <v>18.18048939983071</v>
       </c>
     </row>
     <row r="13">
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.68744859394529</v>
+        <v>16.13625580709803</v>
       </c>
       <c r="C2" t="n">
-        <v>18.39415660140149</v>
+        <v>17.77406471619832</v>
       </c>
       <c r="D2" t="n">
-        <v>20.10086460885771</v>
+        <v>19.41187362529861</v>
       </c>
       <c r="E2" t="n">
-        <v>21.80757261631391</v>
+        <v>21.0496825343989</v>
       </c>
       <c r="F2" t="n">
-        <v>23.5142806237701</v>
+        <v>22.6874914434992</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.19700454656165</v>
+        <v>16.64581175971439</v>
       </c>
       <c r="C3" t="n">
-        <v>18.90371255401786</v>
+        <v>18.28362066881468</v>
       </c>
       <c r="D3" t="n">
-        <v>20.61042056147406</v>
+        <v>19.92142957791497</v>
       </c>
       <c r="E3" t="n">
-        <v>22.31712856893027</v>
+        <v>21.55923848701526</v>
       </c>
       <c r="F3" t="n">
-        <v>24.02383657638646</v>
+        <v>23.19704739611556</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.70656049917802</v>
+        <v>17.15536771233075</v>
       </c>
       <c r="C4" t="n">
-        <v>19.41326850663422</v>
+        <v>18.79317662143104</v>
       </c>
       <c r="D4" t="n">
-        <v>21.11997651409043</v>
+        <v>20.43098553053134</v>
       </c>
       <c r="E4" t="n">
-        <v>22.82668452154663</v>
+        <v>22.06879443963163</v>
       </c>
       <c r="F4" t="n">
-        <v>24.53339252900282</v>
+        <v>23.70660334873193</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.21611645179438</v>
+        <v>17.66492366494712</v>
       </c>
       <c r="C5" t="n">
-        <v>19.92282445925058</v>
+        <v>19.30273257404741</v>
       </c>
       <c r="D5" t="n">
-        <v>21.62953246670679</v>
+        <v>20.9405414831477</v>
       </c>
       <c r="E5" t="n">
-        <v>23.33624047416299</v>
+        <v>22.57835039224799</v>
       </c>
       <c r="F5" t="n">
-        <v>25.04294848161918</v>
+        <v>24.21615930134829</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.72567240441074</v>
+        <v>18.17447961756348</v>
       </c>
       <c r="C6" t="n">
-        <v>20.43238041186695</v>
+        <v>19.81228852666377</v>
       </c>
       <c r="D6" t="n">
-        <v>22.13908841932315</v>
+        <v>21.45009743576406</v>
       </c>
       <c r="E6" t="n">
-        <v>23.84579642677936</v>
+        <v>23.08790634486435</v>
       </c>
       <c r="F6" t="n">
-        <v>25.55250443423555</v>
+        <v>24.72571525396466</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>21.83</v>
+        <v>21.14</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>21.96</v>
+        <v>21.27</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>22.01</v>
+        <v>21.32</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2713.443597791534</v>
+        <v>2713.443597791533</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2713.443597791533</v>
+        <v>2713.443597791534</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.47</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2713.443597791533</v>
+        <v>5949.25882687412</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1283629848710788</v>
+        <v>0.2814374403837691</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -12,7 +12,6 @@
     <sheet name="DivStrip" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Sensitivity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Payout" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Warnings" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1260,35 +1259,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Data validation warnings</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>spot TCE VLCC: $388,300/day is 9.7x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.99</v>
+        <v>17.56</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5949.25882687412</v>
+        <v>3273.488541286598</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2814374403837691</v>
+        <v>0.1548566406328906</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -425,7 +425,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.56</v>
+        <v>18.21</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3273.488541286598</v>
+        <v>7318.257577639833</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1548566406328906</v>
+        <v>0.3461997100237536</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -425,7 +425,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.43098553053134</v>
+        <v>20.42513114194146</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18.18048939983071</v>
+        <v>18.16585342835603</v>
       </c>
     </row>
     <row r="9">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16000</v>
+        <v>17900</v>
       </c>
     </row>
     <row r="10">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16406.25</v>
+        <v>16212.5</v>
       </c>
     </row>
     <row r="11">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.214902242349383</v>
+        <v>1.380825634303155</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7318.257577639833</v>
+        <v>7395.512086386208</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3461997100237536</v>
+        <v>0.3467973735117554</v>
       </c>
     </row>
   </sheetData>
@@ -826,13 +826,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19075</v>
+        <v>18550</v>
       </c>
       <c r="C2" t="n">
-        <v>19075</v>
+        <v>18550</v>
       </c>
       <c r="D2" t="n">
-        <v>1.228072620956282</v>
+        <v>1.179903146638329</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -848,13 +848,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17550</v>
+        <v>17300</v>
       </c>
       <c r="C3" t="n">
-        <v>17550</v>
+        <v>17300</v>
       </c>
       <c r="D3" t="n">
-        <v>1.110376381403969</v>
+        <v>1.10880463272181</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
         <v>14800</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8174763916932639</v>
+        <v>0.8293107347118782</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -898,7 +898,7 @@
         <v>14200</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7357454602209584</v>
+        <v>0.7560857372842019</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -914,13 +914,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13800</v>
+        <v>13600</v>
       </c>
       <c r="C6" t="n">
-        <v>13800</v>
+        <v>13600</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6606713466966236</v>
+        <v>0.6828607398565255</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -936,13 +936,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13500</v>
+        <v>13000</v>
       </c>
       <c r="C7" t="n">
-        <v>13500</v>
+        <v>13000</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6214700854474635</v>
+        <v>0.6096357424288492</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -958,13 +958,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13200</v>
+        <v>12700</v>
       </c>
       <c r="C8" t="n">
-        <v>13200</v>
+        <v>12700</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5770912991276597</v>
+        <v>0.5704344811796891</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -980,13 +980,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13000</v>
+        <v>12400</v>
       </c>
       <c r="C9" t="n">
-        <v>13000</v>
+        <v>12400</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5463959719231287</v>
+        <v>0.533821982465851</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>22.99229230404076</v>
+        <v>22.97378265191321</v>
       </c>
       <c r="F11" t="n">
-        <v>18.18048939983071</v>
+        <v>18.16585342835603</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>18.18048939983071</v>
+        <v>18.16585342835603</v>
       </c>
     </row>
     <row r="13">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16406.25</v>
+        <v>16212.5</v>
       </c>
     </row>
   </sheetData>
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.13625580709803</v>
+        <v>16.13215773508512</v>
       </c>
       <c r="C2" t="n">
-        <v>17.77406471619832</v>
+        <v>17.76996664418541</v>
       </c>
       <c r="D2" t="n">
-        <v>19.41187362529861</v>
+        <v>19.4077755532857</v>
       </c>
       <c r="E2" t="n">
-        <v>21.0496825343989</v>
+        <v>21.04558446238599</v>
       </c>
       <c r="F2" t="n">
-        <v>22.6874914434992</v>
+        <v>22.68339337148629</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.64581175971439</v>
+        <v>16.640835529413</v>
       </c>
       <c r="C3" t="n">
-        <v>18.28362066881468</v>
+        <v>18.27864443851329</v>
       </c>
       <c r="D3" t="n">
-        <v>19.92142957791497</v>
+        <v>19.91645334761358</v>
       </c>
       <c r="E3" t="n">
-        <v>21.55923848701526</v>
+        <v>21.55426225671387</v>
       </c>
       <c r="F3" t="n">
-        <v>23.19704739611556</v>
+        <v>23.19207116581418</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.15536771233075</v>
+        <v>17.14951332374088</v>
       </c>
       <c r="C4" t="n">
-        <v>18.79317662143104</v>
+        <v>18.78732223284117</v>
       </c>
       <c r="D4" t="n">
-        <v>20.43098553053134</v>
+        <v>20.42513114194146</v>
       </c>
       <c r="E4" t="n">
-        <v>22.06879443963163</v>
+        <v>22.06294005104175</v>
       </c>
       <c r="F4" t="n">
-        <v>23.70660334873193</v>
+        <v>23.70074896014206</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17.66492366494712</v>
+        <v>17.65819111806876</v>
       </c>
       <c r="C5" t="n">
-        <v>19.30273257404741</v>
+        <v>19.29600002716905</v>
       </c>
       <c r="D5" t="n">
-        <v>20.9405414831477</v>
+        <v>20.93380893626934</v>
       </c>
       <c r="E5" t="n">
-        <v>22.57835039224799</v>
+        <v>22.57161784536963</v>
       </c>
       <c r="F5" t="n">
-        <v>24.21615930134829</v>
+        <v>24.20942675446994</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.17447961756348</v>
+        <v>18.16686891239664</v>
       </c>
       <c r="C6" t="n">
-        <v>19.81228852666377</v>
+        <v>19.80467782149694</v>
       </c>
       <c r="D6" t="n">
-        <v>21.45009743576406</v>
+        <v>21.44248673059723</v>
       </c>
       <c r="E6" t="n">
-        <v>23.08790634486435</v>
+        <v>23.08029563969752</v>
       </c>
       <c r="F6" t="n">
-        <v>24.72571525396466</v>
+        <v>24.71810454879782</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>21.14</v>
+        <v>21.13</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>21.27</v>
+        <v>21.26</v>
       </c>
     </row>
     <row r="4">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>21.32</v>
+        <v>21.31</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -425,7 +425,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.21</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7395.512086386208</v>
+        <v>7206.859751018284</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3467973735117554</v>
+        <v>0.3379509091089876</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7206.859751018284</v>
+        <v>7206.859751018285</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7206.859751018285</v>
+        <v>7206.859751018284</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.18</v>
+        <v>19.08</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7206.859751018285</v>
+        <v>12866.42981205591</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3379509091089876</v>
+        <v>0.6033448411920181</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.08</v>
+        <v>19.07</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12866.42981205591</v>
+        <v>12803.54570026661</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6033448411920181</v>
+        <v>0.6003960197244294</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.42513114194146</v>
+        <v>20.52475809742018</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18.16585342835603</v>
+        <v>18.41492081705281</v>
       </c>
     </row>
     <row r="9">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17900</v>
+        <v>18350</v>
       </c>
     </row>
     <row r="10">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16212.5</v>
+        <v>16556.25</v>
       </c>
     </row>
     <row r="11">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.380825634303155</v>
+        <v>1.443129382845654</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12803.54570026661</v>
+        <v>12887.72510593475</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6003960197244294</v>
+        <v>0.5832608594162281</v>
       </c>
     </row>
   </sheetData>
@@ -783,8 +783,8 @@
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -826,13 +826,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18550</v>
+        <v>18800</v>
       </c>
       <c r="C2" t="n">
-        <v>18550</v>
+        <v>18800</v>
       </c>
       <c r="D2" t="n">
-        <v>1.179903146638329</v>
+        <v>1.277166653322565</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -848,13 +848,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17300</v>
+        <v>17875</v>
       </c>
       <c r="C3" t="n">
-        <v>17300</v>
+        <v>17875</v>
       </c>
       <c r="D3" t="n">
-        <v>1.10880463272181</v>
+        <v>1.206345506820545</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -870,13 +870,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14800</v>
+        <v>15075</v>
       </c>
       <c r="C4" t="n">
-        <v>14800</v>
+        <v>15075</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8293107347118782</v>
+        <v>0.8718404049350236</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -892,13 +892,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14200</v>
+        <v>14475</v>
       </c>
       <c r="C5" t="n">
-        <v>14200</v>
+        <v>14475</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7560857372842019</v>
+        <v>0.7986154075073473</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -914,13 +914,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13600</v>
+        <v>13875</v>
       </c>
       <c r="C6" t="n">
-        <v>13600</v>
+        <v>13875</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6828607398565255</v>
+        <v>0.7253904100796709</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -936,13 +936,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13000</v>
+        <v>13275</v>
       </c>
       <c r="C7" t="n">
-        <v>13000</v>
+        <v>13275</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6096357424288492</v>
+        <v>0.6521654126519946</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -958,13 +958,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12700</v>
+        <v>12975</v>
       </c>
       <c r="C8" t="n">
-        <v>12700</v>
+        <v>12975</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5704344811796891</v>
+        <v>0.6129641514028344</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -980,13 +980,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12400</v>
+        <v>12675</v>
       </c>
       <c r="C9" t="n">
-        <v>12400</v>
+        <v>12675</v>
       </c>
       <c r="D9" t="n">
-        <v>0.533821982465851</v>
+        <v>0.5763516526889964</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>22.97378265191321</v>
+        <v>23.2887703333985</v>
       </c>
       <c r="F11" t="n">
-        <v>18.16585342835603</v>
+        <v>18.41492081705281</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>18.16585342835603</v>
+        <v>18.41492081705281</v>
       </c>
     </row>
     <row r="13">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16212.5</v>
+        <v>16556.25</v>
       </c>
     </row>
   </sheetData>
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.13215773508512</v>
+        <v>16.20189660392022</v>
       </c>
       <c r="C2" t="n">
-        <v>17.76996664418541</v>
+        <v>17.8397055130205</v>
       </c>
       <c r="D2" t="n">
-        <v>19.4077755532857</v>
+        <v>19.4775144221208</v>
       </c>
       <c r="E2" t="n">
-        <v>21.04558446238599</v>
+        <v>21.11532333122109</v>
       </c>
       <c r="F2" t="n">
-        <v>22.68339337148629</v>
+        <v>22.75313224032139</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.640835529413</v>
+        <v>16.72551844156991</v>
       </c>
       <c r="C3" t="n">
-        <v>18.27864443851329</v>
+        <v>18.3633273506702</v>
       </c>
       <c r="D3" t="n">
-        <v>19.91645334761358</v>
+        <v>20.00113625977049</v>
       </c>
       <c r="E3" t="n">
-        <v>21.55426225671387</v>
+        <v>21.63894516887078</v>
       </c>
       <c r="F3" t="n">
-        <v>23.19207116581418</v>
+        <v>23.27675407797108</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.14951332374088</v>
+        <v>17.2491402792196</v>
       </c>
       <c r="C4" t="n">
-        <v>18.78732223284117</v>
+        <v>18.88694918831989</v>
       </c>
       <c r="D4" t="n">
-        <v>20.42513114194146</v>
+        <v>20.52475809742018</v>
       </c>
       <c r="E4" t="n">
-        <v>22.06294005104175</v>
+        <v>22.16256700652047</v>
       </c>
       <c r="F4" t="n">
-        <v>23.70074896014206</v>
+        <v>23.80037591562077</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17.65819111806876</v>
+        <v>17.77276211686928</v>
       </c>
       <c r="C5" t="n">
-        <v>19.29600002716905</v>
+        <v>19.41057102596957</v>
       </c>
       <c r="D5" t="n">
-        <v>20.93380893626934</v>
+        <v>21.04837993506987</v>
       </c>
       <c r="E5" t="n">
-        <v>22.57161784536963</v>
+        <v>22.68618884417016</v>
       </c>
       <c r="F5" t="n">
-        <v>24.20942675446994</v>
+        <v>24.32399775327046</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.16686891239664</v>
+        <v>18.29638395451897</v>
       </c>
       <c r="C6" t="n">
-        <v>19.80467782149694</v>
+        <v>19.93419286361926</v>
       </c>
       <c r="D6" t="n">
-        <v>21.44248673059723</v>
+        <v>21.57200177271956</v>
       </c>
       <c r="E6" t="n">
-        <v>23.08029563969752</v>
+        <v>23.20981068181985</v>
       </c>
       <c r="F6" t="n">
-        <v>24.71810454879782</v>
+        <v>24.84761959092015</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>21.13</v>
+        <v>21.28</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>21.26</v>
+        <v>21.42</v>
       </c>
     </row>
     <row r="4">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>21.31</v>
+        <v>21.47</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.07</v>
+        <v>19.56</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12887.72510593475</v>
+        <v>15989.30533198687</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5832608594162281</v>
+        <v>0.7236293366552784</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.56</v>
+        <v>19.94</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15989.30533198687</v>
+        <v>18394.61244606812</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7236293366552784</v>
+        <v>0.8324865230855627</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18394.61244606812</v>
+        <v>18394.61244606811</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18394.61244606811</v>
+        <v>18394.61244606812</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.94</v>
+        <v>18.81</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18394.61244606812</v>
+        <v>11241.98865945812</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8324865230855627</v>
+        <v>0.5087796265955078</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.52475809742018</v>
+        <v>20.98136411633931</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31.33045183475965</v>
+        <v>32.10293248877242</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18.41492081705281</v>
+        <v>18.74533117763722</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.443129382845654</v>
+        <v>1.441294461843334</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11241.98865945812</v>
+        <v>8328.440791457666</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5087796265955078</v>
+        <v>0.3779773988937458</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>215.191058659085</v>
+        <v>218.9342314082434</v>
       </c>
     </row>
     <row r="3">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>140.0046718952724</v>
+        <v>141.4165066523644</v>
       </c>
     </row>
     <row r="4">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>302.159382783397</v>
+        <v>315.6833221020438</v>
       </c>
     </row>
     <row r="5">
@@ -722,7 +722,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>757.5851133377544</v>
+        <v>776.2640601626518</v>
       </c>
     </row>
     <row r="12">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31.33045183475965</v>
+        <v>32.10293248877242</v>
       </c>
     </row>
     <row r="14">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31.33045183475965</v>
+        <v>32.10293248877242</v>
       </c>
     </row>
     <row r="15">
@@ -783,8 +783,8 @@
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>23.2887703333985</v>
+        <v>23.70662990933</v>
       </c>
       <c r="F11" t="n">
-        <v>18.41492081705281</v>
+        <v>18.74533117763722</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>18.41492081705281</v>
+        <v>18.74533117763722</v>
       </c>
     </row>
     <row r="13">
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.20189660392022</v>
+        <v>16.56718141905551</v>
       </c>
       <c r="C2" t="n">
-        <v>17.8397055130205</v>
+        <v>18.25065093004772</v>
       </c>
       <c r="D2" t="n">
-        <v>19.4775144221208</v>
+        <v>19.93412044103993</v>
       </c>
       <c r="E2" t="n">
-        <v>21.11532333122109</v>
+        <v>21.61758995203213</v>
       </c>
       <c r="F2" t="n">
-        <v>22.75313224032139</v>
+        <v>23.30105946302434</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.72551844156991</v>
+        <v>17.0908032567052</v>
       </c>
       <c r="C3" t="n">
-        <v>18.3633273506702</v>
+        <v>18.77427276769741</v>
       </c>
       <c r="D3" t="n">
-        <v>20.00113625977049</v>
+        <v>20.45774227868962</v>
       </c>
       <c r="E3" t="n">
-        <v>21.63894516887078</v>
+        <v>22.14121178968182</v>
       </c>
       <c r="F3" t="n">
-        <v>23.27675407797108</v>
+        <v>23.82468130067403</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.2491402792196</v>
+        <v>17.61442509435489</v>
       </c>
       <c r="C4" t="n">
-        <v>18.88694918831989</v>
+        <v>19.2978946053471</v>
       </c>
       <c r="D4" t="n">
-        <v>20.52475809742018</v>
+        <v>20.98136411633931</v>
       </c>
       <c r="E4" t="n">
-        <v>22.16256700652047</v>
+        <v>22.66483362733151</v>
       </c>
       <c r="F4" t="n">
-        <v>23.80037591562077</v>
+        <v>24.34830313832371</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17.77276211686928</v>
+        <v>18.13804693200458</v>
       </c>
       <c r="C5" t="n">
-        <v>19.41057102596957</v>
+        <v>19.82151644299678</v>
       </c>
       <c r="D5" t="n">
-        <v>21.04837993506987</v>
+        <v>21.504985953989</v>
       </c>
       <c r="E5" t="n">
-        <v>22.68618884417016</v>
+        <v>23.1884554649812</v>
       </c>
       <c r="F5" t="n">
-        <v>24.32399775327046</v>
+        <v>24.87192497597341</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.29638395451897</v>
+        <v>18.66166876965427</v>
       </c>
       <c r="C6" t="n">
-        <v>19.93419286361926</v>
+        <v>20.34513828064647</v>
       </c>
       <c r="D6" t="n">
-        <v>21.57200177271956</v>
+        <v>22.02860779163868</v>
       </c>
       <c r="E6" t="n">
-        <v>23.20981068181985</v>
+        <v>23.71207730263089</v>
       </c>
       <c r="F6" t="n">
-        <v>24.84761959092015</v>
+        <v>25.39554681362309</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>21.28</v>
+        <v>21.74</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>21.42</v>
+        <v>21.88</v>
       </c>
     </row>
     <row r="4">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>21.47</v>
+        <v>21.93</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.81</v>
+        <v>18.63</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8328.440791457666</v>
+        <v>7192.269309544708</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3779773988937458</v>
+        <v>0.3264134684794011</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.98136411633931</v>
+        <v>21.01362466325413</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18.74533117763722</v>
+        <v>18.82598254492429</v>
       </c>
     </row>
     <row r="9">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18350</v>
+        <v>18800</v>
       </c>
     </row>
     <row r="10">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16556.25</v>
+        <v>16775</v>
       </c>
     </row>
     <row r="11">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.441294461843334</v>
+        <v>1.450226918105278</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7192.269309544708</v>
+        <v>7185.986714335031</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3264134684794011</v>
+        <v>0.323424521722539</v>
       </c>
     </row>
   </sheetData>
@@ -826,13 +826,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18800</v>
+        <v>19100</v>
       </c>
       <c r="C2" t="n">
-        <v>18800</v>
+        <v>19100</v>
       </c>
       <c r="D2" t="n">
-        <v>1.277166653322565</v>
+        <v>1.269585277326266</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -848,13 +848,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17875</v>
+        <v>18450</v>
       </c>
       <c r="C3" t="n">
-        <v>17875</v>
+        <v>18450</v>
       </c>
       <c r="D3" t="n">
-        <v>1.206345506820545</v>
+        <v>1.248135530605027</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
         <v>15075</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8718404049350236</v>
+        <v>0.8904240217064414</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -898,7 +898,7 @@
         <v>14475</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7986154075073473</v>
+        <v>0.8171990242787651</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>13875</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7253904100796709</v>
+        <v>0.7439740268510887</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -942,7 +942,7 @@
         <v>13275</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6521654126519946</v>
+        <v>0.6707490294234124</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -964,7 +964,7 @@
         <v>12975</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6129641514028344</v>
+        <v>0.6315477681742524</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
         <v>12675</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5763516526889964</v>
+        <v>0.5949352694604142</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>23.70662990933</v>
+        <v>23.80862715322168</v>
       </c>
       <c r="F11" t="n">
-        <v>18.74533117763722</v>
+        <v>18.82598254492429</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>18.74533117763722</v>
+        <v>18.82598254492429</v>
       </c>
     </row>
     <row r="13">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16556.25</v>
+        <v>16775</v>
       </c>
     </row>
   </sheetData>
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.56718141905551</v>
+        <v>16.58976380189589</v>
       </c>
       <c r="C2" t="n">
-        <v>18.25065093004772</v>
+        <v>18.2732333128881</v>
       </c>
       <c r="D2" t="n">
-        <v>19.93412044103993</v>
+        <v>19.95670282388031</v>
       </c>
       <c r="E2" t="n">
-        <v>21.61758995203213</v>
+        <v>21.64017233487251</v>
       </c>
       <c r="F2" t="n">
-        <v>23.30105946302434</v>
+        <v>23.32364184586472</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.0908032567052</v>
+        <v>17.1182247215828</v>
       </c>
       <c r="C3" t="n">
-        <v>18.77427276769741</v>
+        <v>18.80169423257501</v>
       </c>
       <c r="D3" t="n">
-        <v>20.45774227868962</v>
+        <v>20.48516374356722</v>
       </c>
       <c r="E3" t="n">
-        <v>22.14121178968182</v>
+        <v>22.16863325455942</v>
       </c>
       <c r="F3" t="n">
-        <v>23.82468130067403</v>
+        <v>23.85210276555163</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.61442509435489</v>
+        <v>17.64668564126971</v>
       </c>
       <c r="C4" t="n">
-        <v>19.2978946053471</v>
+        <v>19.33015515226192</v>
       </c>
       <c r="D4" t="n">
-        <v>20.98136411633931</v>
+        <v>21.01362466325413</v>
       </c>
       <c r="E4" t="n">
-        <v>22.66483362733151</v>
+        <v>22.69709417424633</v>
       </c>
       <c r="F4" t="n">
-        <v>24.34830313832371</v>
+        <v>24.38056368523854</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.13804693200458</v>
+        <v>18.17514656095663</v>
       </c>
       <c r="C5" t="n">
-        <v>19.82151644299678</v>
+        <v>19.85861607194883</v>
       </c>
       <c r="D5" t="n">
-        <v>21.504985953989</v>
+        <v>21.54208558294104</v>
       </c>
       <c r="E5" t="n">
-        <v>23.1884554649812</v>
+        <v>23.22555509393325</v>
       </c>
       <c r="F5" t="n">
-        <v>24.87192497597341</v>
+        <v>24.90902460492545</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.66166876965427</v>
+        <v>18.70360748064354</v>
       </c>
       <c r="C6" t="n">
-        <v>20.34513828064647</v>
+        <v>20.38707699163574</v>
       </c>
       <c r="D6" t="n">
-        <v>22.02860779163868</v>
+        <v>22.07054650262796</v>
       </c>
       <c r="E6" t="n">
-        <v>23.71207730263089</v>
+        <v>23.75401601362016</v>
       </c>
       <c r="F6" t="n">
-        <v>25.39554681362309</v>
+        <v>25.43748552461237</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>21.74</v>
+        <v>21.79</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>21.88</v>
+        <v>21.93</v>
       </c>
     </row>
     <row r="4">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>21.93</v>
+        <v>21.98</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.63</v>
+        <v>18.84</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7185.986714335031</v>
+        <v>8510.362229208709</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.323424521722539</v>
+        <v>0.3830315784158935</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.01362466325413</v>
+        <v>21.33767209251905</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.10293248877242</v>
+        <v>32.65040504575753</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18.82598254492429</v>
+        <v>19.06125493325222</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.450226918105278</v>
+        <v>1.44894304614805</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8510.362229208709</v>
+        <v>6450.091574358108</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3830315784158935</v>
+        <v>0.2910529427609897</v>
       </c>
     </row>
   </sheetData>
@@ -611,7 +611,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>218.9342314082434</v>
+        <v>220.9268769294548</v>
       </c>
     </row>
     <row r="3">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>141.4165066523644</v>
+        <v>142.0411026448507</v>
       </c>
     </row>
     <row r="4">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>315.6833221020438</v>
+        <v>326.3042254232928</v>
       </c>
     </row>
     <row r="5">
@@ -722,7 +722,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>776.2640601626518</v>
+        <v>789.5022049975986</v>
       </c>
     </row>
     <row r="12">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32.10293248877242</v>
+        <v>32.65040504575753</v>
       </c>
     </row>
     <row r="14">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32.10293248877242</v>
+        <v>32.65040504575753</v>
       </c>
     </row>
     <row r="15">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>23.80862715322168</v>
+        <v>24.10616873224848</v>
       </c>
       <c r="F11" t="n">
-        <v>18.82598254492429</v>
+        <v>19.06125493325222</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>18.82598254492429</v>
+        <v>19.06125493325222</v>
       </c>
     </row>
     <row r="13">
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.58976380189589</v>
+        <v>16.84900174530782</v>
       </c>
       <c r="C2" t="n">
-        <v>18.2732333128881</v>
+        <v>18.56487599922652</v>
       </c>
       <c r="D2" t="n">
-        <v>19.95670282388031</v>
+        <v>20.28075025314523</v>
       </c>
       <c r="E2" t="n">
-        <v>21.64017233487251</v>
+        <v>21.99662450706392</v>
       </c>
       <c r="F2" t="n">
-        <v>23.32364184586472</v>
+        <v>23.71249876098262</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.1182247215828</v>
+        <v>17.37746266499473</v>
       </c>
       <c r="C3" t="n">
-        <v>18.80169423257501</v>
+        <v>19.09333691891343</v>
       </c>
       <c r="D3" t="n">
-        <v>20.48516374356722</v>
+        <v>20.80921117283214</v>
       </c>
       <c r="E3" t="n">
-        <v>22.16863325455942</v>
+        <v>22.52508542675083</v>
       </c>
       <c r="F3" t="n">
-        <v>23.85210276555163</v>
+        <v>24.24095968066953</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.64668564126971</v>
+        <v>17.90592358468164</v>
       </c>
       <c r="C4" t="n">
-        <v>19.33015515226192</v>
+        <v>19.62179783860035</v>
       </c>
       <c r="D4" t="n">
-        <v>21.01362466325413</v>
+        <v>21.33767209251905</v>
       </c>
       <c r="E4" t="n">
-        <v>22.69709417424633</v>
+        <v>23.05354634643775</v>
       </c>
       <c r="F4" t="n">
-        <v>24.38056368523854</v>
+        <v>24.76942060035644</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.17514656095663</v>
+        <v>18.43438450436856</v>
       </c>
       <c r="C5" t="n">
-        <v>19.85861607194883</v>
+        <v>20.15025875828726</v>
       </c>
       <c r="D5" t="n">
-        <v>21.54208558294104</v>
+        <v>21.86613301220596</v>
       </c>
       <c r="E5" t="n">
-        <v>23.22555509393325</v>
+        <v>23.58200726612466</v>
       </c>
       <c r="F5" t="n">
-        <v>24.90902460492545</v>
+        <v>25.29788152004335</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.70360748064354</v>
+        <v>18.96284542405547</v>
       </c>
       <c r="C6" t="n">
-        <v>20.38707699163574</v>
+        <v>20.67871967797418</v>
       </c>
       <c r="D6" t="n">
-        <v>22.07054650262796</v>
+        <v>22.39459393189288</v>
       </c>
       <c r="E6" t="n">
-        <v>23.75401601362016</v>
+        <v>24.11046818581157</v>
       </c>
       <c r="F6" t="n">
-        <v>25.43748552461237</v>
+        <v>25.82634243973027</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>21.79</v>
+        <v>22.11</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>21.93</v>
+        <v>22.26</v>
       </c>
     </row>
     <row r="4">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>21.98</v>
+        <v>22.3</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -425,7 +425,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.84</v>
+        <v>19.305</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6450.091574358108</v>
+        <v>9375.087204164065</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2910529427609897</v>
+        <v>0.4230399968677028</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9375.087204164065</v>
+        <v>9375.087204164063</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9375.087204164063</v>
+        <v>9375.087204164065</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -425,7 +425,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.305</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9375.087204164065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4230399968677028</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -425,7 +425,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>2026-Q2</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.33767209251905</v>
+        <v>20.8682548654576</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.65040504575753</v>
+        <v>31.92053068117769</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19.06125493325222</v>
+        <v>18.65407994840743</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.44894304614805</v>
+        <v>1.446956601635411</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2798.381943988648</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.1268936529165119</v>
       </c>
     </row>
   </sheetData>
@@ -611,7 +611,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>220.9268769294548</v>
+        <v>214.0976747849028</v>
       </c>
     </row>
     <row r="3">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>142.0411026448507</v>
+        <v>137.6799098168538</v>
       </c>
     </row>
     <row r="4">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>326.3042254232928</v>
+        <v>329.8966203034917</v>
       </c>
     </row>
     <row r="5">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>258.455</v>
+        <v>234.781</v>
       </c>
     </row>
     <row r="6">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.786</v>
+        <v>29.553</v>
       </c>
     </row>
     <row r="7">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-141.363</v>
+        <v>-137.881</v>
       </c>
     </row>
     <row r="8">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-20.648</v>
+        <v>-34.321</v>
       </c>
     </row>
     <row r="9">
@@ -722,7 +722,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>789.5022049975986</v>
+        <v>773.8062049052484</v>
       </c>
     </row>
     <row r="12">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24180472</v>
+        <v>24241646</v>
       </c>
     </row>
     <row r="13">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32.65040504575753</v>
+        <v>31.92053068117769</v>
       </c>
     </row>
     <row r="14">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32.65040504575753</v>
+        <v>31.92053068117769</v>
       </c>
     </row>
     <row r="15">
@@ -832,7 +832,7 @@
         <v>19100</v>
       </c>
       <c r="D2" t="n">
-        <v>1.269585277326266</v>
+        <v>1.266381468073579</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -854,7 +854,7 @@
         <v>18450</v>
       </c>
       <c r="D3" t="n">
-        <v>1.248135530605027</v>
+        <v>1.244985849970749</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
         <v>15075</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8904240217064414</v>
+        <v>0.8881770291093269</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -898,7 +898,7 @@
         <v>14475</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8171990242787651</v>
+        <v>0.8151368155858724</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>13875</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7439740268510887</v>
+        <v>0.7420966020624177</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -942,7 +942,7 @@
         <v>13275</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6707490294234124</v>
+        <v>0.6690563885389631</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -964,7 +964,7 @@
         <v>12975</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6315477681742524</v>
+        <v>0.6299540520062046</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
         <v>12675</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5949352694604142</v>
+        <v>0.5934339452444772</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>24.10616873224848</v>
+        <v>23.59122735390847</v>
       </c>
       <c r="F11" t="n">
-        <v>19.06125493325222</v>
+        <v>18.65407994840743</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>19.06125493325222</v>
+        <v>18.65407994840743</v>
       </c>
     </row>
     <row r="13">
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.84900174530782</v>
+        <v>16.4311735280417</v>
       </c>
       <c r="C2" t="n">
-        <v>18.56487599922652</v>
+        <v>18.12258685269126</v>
       </c>
       <c r="D2" t="n">
-        <v>20.28075025314523</v>
+        <v>19.81400017734082</v>
       </c>
       <c r="E2" t="n">
-        <v>21.99662450706392</v>
+        <v>21.50541350199039</v>
       </c>
       <c r="F2" t="n">
-        <v>23.71249876098262</v>
+        <v>23.19682682663995</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.37746266499473</v>
+        <v>16.95830087210009</v>
       </c>
       <c r="C3" t="n">
-        <v>19.09333691891343</v>
+        <v>18.64971419674965</v>
       </c>
       <c r="D3" t="n">
-        <v>20.80921117283214</v>
+        <v>20.34112752139921</v>
       </c>
       <c r="E3" t="n">
-        <v>22.52508542675083</v>
+        <v>22.03254084604878</v>
       </c>
       <c r="F3" t="n">
-        <v>24.24095968066953</v>
+        <v>23.72395417069834</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.90592358468164</v>
+        <v>17.48542821615848</v>
       </c>
       <c r="C4" t="n">
-        <v>19.62179783860035</v>
+        <v>19.17684154080804</v>
       </c>
       <c r="D4" t="n">
-        <v>21.33767209251905</v>
+        <v>20.8682548654576</v>
       </c>
       <c r="E4" t="n">
-        <v>23.05354634643775</v>
+        <v>22.55966819010717</v>
       </c>
       <c r="F4" t="n">
-        <v>24.76942060035644</v>
+        <v>24.25108151475673</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.43438450436856</v>
+        <v>18.01255556021687</v>
       </c>
       <c r="C5" t="n">
-        <v>20.15025875828726</v>
+        <v>19.70396888486643</v>
       </c>
       <c r="D5" t="n">
-        <v>21.86613301220596</v>
+        <v>21.39538220951599</v>
       </c>
       <c r="E5" t="n">
-        <v>23.58200726612466</v>
+        <v>23.08679553416555</v>
       </c>
       <c r="F5" t="n">
-        <v>25.29788152004335</v>
+        <v>24.77820885881511</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.96284542405547</v>
+        <v>18.53968290427526</v>
       </c>
       <c r="C6" t="n">
-        <v>20.67871967797418</v>
+        <v>20.23109622892481</v>
       </c>
       <c r="D6" t="n">
-        <v>22.39459393189288</v>
+        <v>21.92250955357438</v>
       </c>
       <c r="E6" t="n">
-        <v>24.11046818581157</v>
+        <v>23.61392287822394</v>
       </c>
       <c r="F6" t="n">
-        <v>25.82634243973027</v>
+        <v>25.3053362028735</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>22.11</v>
+        <v>21.64</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>22.26</v>
+        <v>21.78</v>
       </c>
     </row>
     <row r="4">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>22.3</v>
+        <v>21.83</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.8682548654576</v>
+        <v>21.16267853490669</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31.92053068117769</v>
+        <v>32.42528831102706</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18.65407994840743</v>
+        <v>18.86014361068832</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.446956601635411</v>
+        <v>1.449374549514792</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2798.381943988648</v>
+        <v>949.0287065295829</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1268936529165119</v>
+        <v>0.04311209440857078</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>214.0976747849028</v>
+        <v>215.5738716297373</v>
       </c>
     </row>
     <row r="3">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>137.6799098168538</v>
+        <v>147.917054717061</v>
       </c>
     </row>
     <row r="4">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>329.8966203034917</v>
+        <v>330.4194343370576</v>
       </c>
     </row>
     <row r="5">
@@ -722,7 +722,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>773.8062049052484</v>
+        <v>786.0423606838559</v>
       </c>
     </row>
     <row r="12">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31.92053068117769</v>
+        <v>32.42528831102706</v>
       </c>
     </row>
     <row r="14">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31.92053068117769</v>
+        <v>32.42528831102706</v>
       </c>
     </row>
     <row r="15">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>23.59122735390847</v>
+        <v>23.85182957710536</v>
       </c>
       <c r="F11" t="n">
-        <v>18.65407994840743</v>
+        <v>18.86014361068832</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>18.65407994840743</v>
+        <v>18.86014361068832</v>
       </c>
     </row>
     <row r="13">
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.4311735280417</v>
+        <v>16.66671246360097</v>
       </c>
       <c r="C2" t="n">
-        <v>18.12258685269126</v>
+        <v>18.38756815519545</v>
       </c>
       <c r="D2" t="n">
-        <v>19.81400017734082</v>
+        <v>20.10842384678991</v>
       </c>
       <c r="E2" t="n">
-        <v>21.50541350199039</v>
+        <v>21.82927953838439</v>
       </c>
       <c r="F2" t="n">
-        <v>23.19682682663995</v>
+        <v>23.55013522997885</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.95830087210009</v>
+        <v>17.19383980765936</v>
       </c>
       <c r="C3" t="n">
-        <v>18.64971419674965</v>
+        <v>18.91469549925383</v>
       </c>
       <c r="D3" t="n">
-        <v>20.34112752139921</v>
+        <v>20.6355511908483</v>
       </c>
       <c r="E3" t="n">
-        <v>22.03254084604878</v>
+        <v>22.35640688244278</v>
       </c>
       <c r="F3" t="n">
-        <v>23.72395417069834</v>
+        <v>24.07726257403724</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.48542821615848</v>
+        <v>17.72096715171775</v>
       </c>
       <c r="C4" t="n">
-        <v>19.17684154080804</v>
+        <v>19.44182284331222</v>
       </c>
       <c r="D4" t="n">
-        <v>20.8682548654576</v>
+        <v>21.16267853490669</v>
       </c>
       <c r="E4" t="n">
-        <v>22.55966819010717</v>
+        <v>22.88353422650116</v>
       </c>
       <c r="F4" t="n">
-        <v>24.25108151475673</v>
+        <v>24.60438991809563</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.01255556021687</v>
+        <v>18.24809449577614</v>
       </c>
       <c r="C5" t="n">
-        <v>19.70396888486643</v>
+        <v>19.96895018737061</v>
       </c>
       <c r="D5" t="n">
-        <v>21.39538220951599</v>
+        <v>21.68980587896508</v>
       </c>
       <c r="E5" t="n">
-        <v>23.08679553416555</v>
+        <v>23.41066157055955</v>
       </c>
       <c r="F5" t="n">
-        <v>24.77820885881511</v>
+        <v>25.13151726215402</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.53968290427526</v>
+        <v>18.77522183983453</v>
       </c>
       <c r="C6" t="n">
-        <v>20.23109622892481</v>
+        <v>20.496077531429</v>
       </c>
       <c r="D6" t="n">
-        <v>21.92250955357438</v>
+        <v>22.21693322302347</v>
       </c>
       <c r="E6" t="n">
-        <v>23.61392287822394</v>
+        <v>23.93778891461794</v>
       </c>
       <c r="F6" t="n">
-        <v>25.3053362028735</v>
+        <v>25.65864460621241</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>21.64</v>
+        <v>21.93</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>21.78</v>
+        <v>22.08</v>
       </c>
     </row>
     <row r="4">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>21.83</v>
+        <v>22.13</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.16267853490669</v>
+        <v>21.29580787228945</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18.86014361068832</v>
+        <v>19.19296695414522</v>
       </c>
     </row>
     <row r="9">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18800</v>
+        <v>16750</v>
       </c>
     </row>
     <row r="10">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16775</v>
+        <v>16977</v>
       </c>
     </row>
     <row r="11">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.449374549514792</v>
+        <v>1.314813389522852</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>949.0287065295829</v>
+        <v>929.772732407589</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04311209440857078</v>
+        <v>0.04153847385121355</v>
       </c>
     </row>
   </sheetData>
@@ -826,13 +826,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19100</v>
+        <v>19200</v>
       </c>
       <c r="C2" t="n">
-        <v>19100</v>
+        <v>19200</v>
       </c>
       <c r="D2" t="n">
-        <v>1.266381468073579</v>
+        <v>1.393464061805044</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -848,13 +848,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18450</v>
+        <v>19158</v>
       </c>
       <c r="C3" t="n">
-        <v>18450</v>
+        <v>19158</v>
       </c>
       <c r="D3" t="n">
-        <v>1.244985849970749</v>
+        <v>1.352159452167563</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
         <v>15075</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8881770291093269</v>
+        <v>0.7541777484911709</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -898,7 +898,7 @@
         <v>14475</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8151368155858724</v>
+        <v>0.8617091739562569</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>13875</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7420966020624177</v>
+        <v>0.8274946294900932</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -942,7 +942,7 @@
         <v>13275</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6690563885389631</v>
+        <v>0.7920811926302365</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -964,7 +964,7 @@
         <v>12975</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6299540520062046</v>
+        <v>0.7529788560974778</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
         <v>12675</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5934339452444772</v>
+        <v>0.7164587493357506</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>23.85182957710536</v>
+        <v>24.27274077647276</v>
       </c>
       <c r="F11" t="n">
-        <v>18.86014361068832</v>
+        <v>19.19296695414522</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>18.86014361068832</v>
+        <v>19.19296695414522</v>
       </c>
     </row>
     <row r="13">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16775</v>
+        <v>16977</v>
       </c>
     </row>
   </sheetData>
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.66671246360097</v>
+        <v>16.7599029997689</v>
       </c>
       <c r="C2" t="n">
-        <v>18.38756815519545</v>
+        <v>18.48075869136338</v>
       </c>
       <c r="D2" t="n">
-        <v>20.10842384678991</v>
+        <v>20.20161438295785</v>
       </c>
       <c r="E2" t="n">
-        <v>21.82927953838439</v>
+        <v>21.92247007455232</v>
       </c>
       <c r="F2" t="n">
-        <v>23.55013522997885</v>
+        <v>23.64332576614678</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.19383980765936</v>
+        <v>17.30699974443471</v>
       </c>
       <c r="C3" t="n">
-        <v>18.91469549925383</v>
+        <v>19.02785543602918</v>
       </c>
       <c r="D3" t="n">
-        <v>20.6355511908483</v>
+        <v>20.74871112762365</v>
       </c>
       <c r="E3" t="n">
-        <v>22.35640688244278</v>
+        <v>22.46956681921812</v>
       </c>
       <c r="F3" t="n">
-        <v>24.07726257403724</v>
+        <v>24.19042251081259</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.72096715171775</v>
+        <v>17.85409648910051</v>
       </c>
       <c r="C4" t="n">
-        <v>19.44182284331222</v>
+        <v>19.57495218069498</v>
       </c>
       <c r="D4" t="n">
-        <v>21.16267853490669</v>
+        <v>21.29580787228945</v>
       </c>
       <c r="E4" t="n">
-        <v>22.88353422650116</v>
+        <v>23.01666356388392</v>
       </c>
       <c r="F4" t="n">
-        <v>24.60438991809563</v>
+        <v>24.73751925547839</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.24809449577614</v>
+        <v>18.40119323376631</v>
       </c>
       <c r="C5" t="n">
-        <v>19.96895018737061</v>
+        <v>20.12204892536078</v>
       </c>
       <c r="D5" t="n">
-        <v>21.68980587896508</v>
+        <v>21.84290461695525</v>
       </c>
       <c r="E5" t="n">
-        <v>23.41066157055955</v>
+        <v>23.56376030854972</v>
       </c>
       <c r="F5" t="n">
-        <v>25.13151726215402</v>
+        <v>25.28461600014419</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.77522183983453</v>
+        <v>18.94828997843211</v>
       </c>
       <c r="C6" t="n">
-        <v>20.496077531429</v>
+        <v>20.66914567002658</v>
       </c>
       <c r="D6" t="n">
-        <v>22.21693322302347</v>
+        <v>22.39000136162105</v>
       </c>
       <c r="E6" t="n">
-        <v>23.93778891461794</v>
+        <v>24.11085705321553</v>
       </c>
       <c r="F6" t="n">
-        <v>25.65864460621241</v>
+        <v>25.83171274480999</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>21.93</v>
+        <v>22.13</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>22.08</v>
+        <v>22.29</v>
       </c>
     </row>
     <row r="4">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>22.13</v>
+        <v>22.34</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.29580787228945</v>
+        <v>21.1251310878957</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.42528831102706</v>
+        <v>32.13327642897661</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19.19296695414522</v>
+        <v>19.07288746931379</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.314813389522852</v>
+        <v>1.315971561093412</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>929.772732407589</v>
+        <v>1982.131655726781</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04153847385121355</v>
+        <v>0.08833370323007217</v>
       </c>
     </row>
   </sheetData>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>330.4194343370576</v>
+        <v>323.340585664597</v>
       </c>
     </row>
     <row r="5">
@@ -722,7 +722,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>786.0423606838559</v>
+        <v>778.9635120113952</v>
       </c>
     </row>
     <row r="12">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32.42528831102706</v>
+        <v>32.13327642897661</v>
       </c>
     </row>
     <row r="14">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32.42528831102706</v>
+        <v>32.13327642897661</v>
       </c>
     </row>
     <row r="15">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>24.27274077647276</v>
+        <v>24.12088003420978</v>
       </c>
       <c r="F11" t="n">
-        <v>19.19296695414522</v>
+        <v>19.07288746931379</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>19.19296695414522</v>
+        <v>19.07288746931379</v>
       </c>
     </row>
     <row r="13">
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.7599029997689</v>
+        <v>16.6233615722539</v>
       </c>
       <c r="C2" t="n">
-        <v>18.48075869136338</v>
+        <v>18.327149585409</v>
       </c>
       <c r="D2" t="n">
-        <v>20.20161438295785</v>
+        <v>20.03093759856409</v>
       </c>
       <c r="E2" t="n">
-        <v>21.92247007455232</v>
+        <v>21.73472561171919</v>
       </c>
       <c r="F2" t="n">
-        <v>23.64332576614678</v>
+        <v>23.43851362487428</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.30699974443471</v>
+        <v>17.17045831691971</v>
       </c>
       <c r="C3" t="n">
-        <v>19.02785543602918</v>
+        <v>18.8742463300748</v>
       </c>
       <c r="D3" t="n">
-        <v>20.74871112762365</v>
+        <v>20.57803434322989</v>
       </c>
       <c r="E3" t="n">
-        <v>22.46956681921812</v>
+        <v>22.28182235638499</v>
       </c>
       <c r="F3" t="n">
-        <v>24.19042251081259</v>
+        <v>23.98561036954008</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.85409648910051</v>
+        <v>17.71755506158551</v>
       </c>
       <c r="C4" t="n">
-        <v>19.57495218069498</v>
+        <v>19.4213430747406</v>
       </c>
       <c r="D4" t="n">
-        <v>21.29580787228945</v>
+        <v>21.1251310878957</v>
       </c>
       <c r="E4" t="n">
-        <v>23.01666356388392</v>
+        <v>22.82891910105079</v>
       </c>
       <c r="F4" t="n">
-        <v>24.73751925547839</v>
+        <v>24.53270711420588</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.40119323376631</v>
+        <v>18.26465180625131</v>
       </c>
       <c r="C5" t="n">
-        <v>20.12204892536078</v>
+        <v>19.9684398194064</v>
       </c>
       <c r="D5" t="n">
-        <v>21.84290461695525</v>
+        <v>21.6722278325615</v>
       </c>
       <c r="E5" t="n">
-        <v>23.56376030854972</v>
+        <v>23.3760158457166</v>
       </c>
       <c r="F5" t="n">
-        <v>25.28461600014419</v>
+        <v>25.07980385887168</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.94828997843211</v>
+        <v>18.81174855091711</v>
       </c>
       <c r="C6" t="n">
-        <v>20.66914567002658</v>
+        <v>20.51553656407221</v>
       </c>
       <c r="D6" t="n">
-        <v>22.39000136162105</v>
+        <v>22.2193245772273</v>
       </c>
       <c r="E6" t="n">
-        <v>24.11085705321553</v>
+        <v>23.9231125903824</v>
       </c>
       <c r="F6" t="n">
-        <v>25.83171274480999</v>
+        <v>25.62690060353749</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>22.13</v>
+        <v>21.96</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>22.29</v>
+        <v>22.11</v>
       </c>
     </row>
     <row r="4">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>22.34</v>
+        <v>22.17</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.8</v>
+        <v>17.68</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1982.131655726781</v>
+        <v>1243.862993325157</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.08833370323007217</v>
+        <v>0.05543275805812513</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -425,7 +425,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.68</v>
+        <v>18.23</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1243.862993325157</v>
+        <v>4627.594362665895</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05543275805812513</v>
+        <v>0.2062287567628806</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.23</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4627.594362665895</v>
+        <v>19208.40044509777</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2062287567628806</v>
+        <v>0.856022423908825</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20.6</v>
+        <v>20.52</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19208.40044509777</v>
+        <v>18716.22133683004</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.856022423908825</v>
+        <v>0.8340884604608612</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18716.22133683004</v>
+        <v>18716.22133683003</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.1251310878957</v>
+        <v>21.47687782324793</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.13327642897661</v>
+        <v>32.20169720069602</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19.07288746931379</v>
+        <v>19.88041249738901</v>
       </c>
     </row>
     <row r="9">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16750</v>
+        <v>17713</v>
       </c>
     </row>
     <row r="10">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16977</v>
+        <v>17689.75</v>
       </c>
     </row>
     <row r="11">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.315971561093412</v>
+        <v>1.423698240086844</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18716.22133683003</v>
+        <v>18155.56736192454</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8340884604608612</v>
+        <v>0.7583176639415377</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>147.917054717061</v>
+        <v>149.5756868441296</v>
       </c>
     </row>
     <row r="4">
@@ -722,7 +722,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>778.9635120113952</v>
+        <v>780.6221441384637</v>
       </c>
     </row>
     <row r="12">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32.13327642897661</v>
+        <v>32.20169720069602</v>
       </c>
     </row>
     <row r="14">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32.13327642897661</v>
+        <v>32.20169720069602</v>
       </c>
     </row>
     <row r="15">
@@ -826,13 +826,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19200</v>
+        <v>19450</v>
       </c>
       <c r="C2" t="n">
-        <v>19200</v>
+        <v>19450</v>
       </c>
       <c r="D2" t="n">
-        <v>1.393464061805044</v>
+        <v>1.465467694520413</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -848,13 +848,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19158</v>
+        <v>20275</v>
       </c>
       <c r="C3" t="n">
-        <v>19158</v>
+        <v>20275</v>
       </c>
       <c r="D3" t="n">
-        <v>1.352159452167563</v>
+        <v>1.563843270997357</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -870,13 +870,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15075</v>
+        <v>15150</v>
       </c>
       <c r="C4" t="n">
-        <v>15075</v>
+        <v>15150</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7541777484911709</v>
+        <v>0.8507346974293742</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -892,13 +892,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14475</v>
+        <v>15884</v>
       </c>
       <c r="C5" t="n">
-        <v>14475</v>
+        <v>15884</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8617091739562569</v>
+        <v>1.018882122319581</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -914,13 +914,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13875</v>
+        <v>15883</v>
       </c>
       <c r="C6" t="n">
-        <v>13875</v>
+        <v>15883</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8274946294900932</v>
+        <v>1.018797277627105</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -936,13 +936,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13275</v>
+        <v>15883</v>
       </c>
       <c r="C7" t="n">
-        <v>13275</v>
+        <v>15883</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7920811926302365</v>
+        <v>1.018797277627105</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -958,13 +958,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12975</v>
+        <v>15583</v>
       </c>
       <c r="C8" t="n">
-        <v>12975</v>
+        <v>15583</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7529788560974778</v>
+        <v>0.9796949410943463</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -980,13 +980,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12675</v>
+        <v>15283</v>
       </c>
       <c r="C9" t="n">
-        <v>12675</v>
+        <v>15283</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7164587493357506</v>
+        <v>0.9431748343326189</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>24.12088003420978</v>
+        <v>25.1421315021987</v>
       </c>
       <c r="F11" t="n">
-        <v>19.07288746931379</v>
+        <v>19.88041249738901</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>19.07288746931379</v>
+        <v>19.88041249738901</v>
       </c>
     </row>
     <row r="13">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16977</v>
+        <v>17689.75</v>
       </c>
     </row>
   </sheetData>
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.6233615722539</v>
+        <v>16.87356635079074</v>
       </c>
       <c r="C2" t="n">
-        <v>18.327149585409</v>
+        <v>18.58133642773611</v>
       </c>
       <c r="D2" t="n">
-        <v>20.03093759856409</v>
+        <v>20.28910650468148</v>
       </c>
       <c r="E2" t="n">
-        <v>21.73472561171919</v>
+        <v>21.99687658162685</v>
       </c>
       <c r="F2" t="n">
-        <v>23.43851362487428</v>
+        <v>23.70464665857222</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.17045831691971</v>
+        <v>17.46745201007397</v>
       </c>
       <c r="C3" t="n">
-        <v>18.8742463300748</v>
+        <v>19.17522208701934</v>
       </c>
       <c r="D3" t="n">
-        <v>20.57803434322989</v>
+        <v>20.88299216396471</v>
       </c>
       <c r="E3" t="n">
-        <v>22.28182235638499</v>
+        <v>22.59076224091007</v>
       </c>
       <c r="F3" t="n">
-        <v>23.98561036954008</v>
+        <v>24.29853231785544</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.71755506158551</v>
+        <v>18.06133766935719</v>
       </c>
       <c r="C4" t="n">
-        <v>19.4213430747406</v>
+        <v>19.76910774630257</v>
       </c>
       <c r="D4" t="n">
-        <v>21.1251310878957</v>
+        <v>21.47687782324793</v>
       </c>
       <c r="E4" t="n">
-        <v>22.82891910105079</v>
+        <v>23.1846479001933</v>
       </c>
       <c r="F4" t="n">
-        <v>24.53270711420588</v>
+        <v>24.89241797713867</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.26465180625131</v>
+        <v>18.65522332864042</v>
       </c>
       <c r="C5" t="n">
-        <v>19.9684398194064</v>
+        <v>20.36299340558579</v>
       </c>
       <c r="D5" t="n">
-        <v>21.6722278325615</v>
+        <v>22.07076348253116</v>
       </c>
       <c r="E5" t="n">
-        <v>23.3760158457166</v>
+        <v>23.77853355947653</v>
       </c>
       <c r="F5" t="n">
-        <v>25.07980385887168</v>
+        <v>25.48630363642189</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.81174855091711</v>
+        <v>19.24910898792365</v>
       </c>
       <c r="C6" t="n">
-        <v>20.51553656407221</v>
+        <v>20.95687906486901</v>
       </c>
       <c r="D6" t="n">
-        <v>22.2193245772273</v>
+        <v>22.66464914181439</v>
       </c>
       <c r="E6" t="n">
-        <v>23.9231125903824</v>
+        <v>24.37241921875975</v>
       </c>
       <c r="F6" t="n">
-        <v>25.62690060353749</v>
+        <v>26.08018929570513</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>21.96</v>
+        <v>22.46</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>22.11</v>
+        <v>22.64</v>
       </c>
     </row>
     <row r="4">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>22.17</v>
+        <v>22.7</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmdb_fv_report.xlsx
+++ b/outputs/cmdb_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.47687782324793</v>
+        <v>21.83317940331863</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.20169720069602</v>
+        <v>32.60095609343131</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19.88041249738901</v>
+        <v>20.3519446101937</v>
       </c>
     </row>
     <row r="9">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17713</v>
+        <v>18467</v>
       </c>
     </row>
     <row r="10">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17689.75</v>
+        <v>18243.75</v>
       </c>
     </row>
     <row r="11">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.423698240086844</v>
+        <v>1.490771051491501</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18155.56736192454</v>
+        <v>16930.56640592407</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7583176639415377</v>
+        <v>0.6782888243454288</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>149.5756868441296</v>
+        <v>152.1415134988642</v>
       </c>
     </row>
     <row r="4">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>323.340585664597</v>
+        <v>330.4534517499033</v>
       </c>
     </row>
     <row r="5">
@@ -722,7 +722,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>780.6221441384637</v>
+        <v>790.3008368785049</v>
       </c>
     </row>
     <row r="12">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32.20169720069602</v>
+        <v>32.60095609343131</v>
       </c>
     </row>
     <row r="14">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32.20169720069602</v>
+        <v>32.60095609343131</v>
       </c>
     </row>
     <row r="15">
@@ -783,7 +783,7 @@
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -826,13 +826,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19450</v>
+        <v>19875</v>
       </c>
       <c r="C2" t="n">
-        <v>19450</v>
+        <v>19875</v>
       </c>
       <c r="D2" t="n">
-        <v>1.465467694520413</v>
+        <v>1.612215812408118</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -848,13 +848,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20275</v>
+        <v>20933</v>
       </c>
       <c r="C3" t="n">
-        <v>20275</v>
+        <v>20933</v>
       </c>
       <c r="D3" t="n">
-        <v>1.563843270997357</v>
+        <v>1.683330420302318</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -870,13 +870,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15150</v>
+        <v>16000</v>
       </c>
       <c r="C4" t="n">
-        <v>15150</v>
+        <v>16000</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8507346974293742</v>
+        <v>0.9531938858442203</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -892,13 +892,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15884</v>
+        <v>16167</v>
       </c>
       <c r="C5" t="n">
-        <v>15884</v>
+        <v>16167</v>
       </c>
       <c r="D5" t="n">
-        <v>1.018882122319581</v>
+        <v>1.055911297236169</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -914,13 +914,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15883</v>
+        <v>16167</v>
       </c>
       <c r="C6" t="n">
-        <v>15883</v>
+        <v>16167</v>
       </c>
       <c r="D6" t="n">
-        <v>1.018797277627105</v>
+        <v>1.055889163838132</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -936,13 +936,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15883</v>
+        <v>16166</v>
       </c>
       <c r="C7" t="n">
-        <v>15883</v>
+        <v>16166</v>
       </c>
       <c r="D7" t="n">
-        <v>1.018797277627105</v>
+        <v>1.055804319145655</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -958,13 +958,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15583</v>
+        <v>15866</v>
       </c>
       <c r="C8" t="n">
-        <v>15583</v>
+        <v>15866</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9796949410943463</v>
+        <v>1.016701982612897</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -980,13 +980,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15283</v>
+        <v>15566</v>
       </c>
       <c r="C9" t="n">
-        <v>15283</v>
+        <v>15566</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9431748343326189</v>
+        <v>0.9801818758511693</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>25.1421315021987</v>
+        <v>25.73846331318109</v>
       </c>
       <c r="F11" t="n">
-        <v>19.88041249738901</v>
+        <v>20.3519446101937</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>19.88041249738901</v>
+        <v>20.3519446101937</v>
       </c>
     </row>
     <row r="13">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17689.75</v>
+        <v>18243.75</v>
       </c>
     </row>
   </sheetData>
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.87356635079074</v>
+        <v>17.14634556678849</v>
       </c>
       <c r="C2" t="n">
-        <v>18.58133642773611</v>
+        <v>18.87748375368213</v>
       </c>
       <c r="D2" t="n">
-        <v>20.28910650468148</v>
+        <v>20.60862194057575</v>
       </c>
       <c r="E2" t="n">
-        <v>21.99687658162685</v>
+        <v>22.33976012746939</v>
       </c>
       <c r="F2" t="n">
-        <v>23.70464665857222</v>
+        <v>24.07089831436302</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.46745201007397</v>
+        <v>17.75862429815993</v>
       </c>
       <c r="C3" t="n">
-        <v>19.17522208701934</v>
+        <v>19.48976248505356</v>
       </c>
       <c r="D3" t="n">
-        <v>20.88299216396471</v>
+        <v>21.22090067194719</v>
       </c>
       <c r="E3" t="n">
-        <v>22.59076224091007</v>
+        <v>22.95203885884083</v>
       </c>
       <c r="F3" t="n">
-        <v>24.29853231785544</v>
+        <v>24.68317704573446</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.06133766935719</v>
+        <v>18.37090302953137</v>
       </c>
       <c r="C4" t="n">
-        <v>19.76910774630257</v>
+        <v>20.102041216425</v>
       </c>
       <c r="D4" t="n">
-        <v>21.47687782324793</v>
+        <v>21.83317940331863</v>
       </c>
       <c r="E4" t="n">
-        <v>23.1846479001933</v>
+        <v>23.56431759021227</v>
       </c>
       <c r="F4" t="n">
-        <v>24.89241797713867</v>
+        <v>25.2954557771059</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.65522332864042</v>
+        <v>18.98318176090281</v>
       </c>
       <c r="C5" t="n">
-        <v>20.36299340558579</v>
+        <v>20.71431994779644</v>
       </c>
       <c r="D5" t="n">
-        <v>22.07076348253116</v>
+        <v>22.44545813469006</v>
       </c>
       <c r="E5" t="n">
-        <v>23.77853355947653</v>
+        <v>24.17659632158371</v>
       </c>
       <c r="F5" t="n">
-        <v>25.48630363642189</v>
+        <v>25.90773450847733</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.24910898792365</v>
+        <v>19.59546049227425</v>
       </c>
       <c r="C6" t="n">
-        <v>20.95687906486901</v>
+        <v>21.32659867916788</v>
       </c>
       <c r="D6" t="n">
-        <v>22.66464914181439</v>
+        <v>23.0577368660615</v>
       </c>
       <c r="E6" t="n">
-        <v>24.37241921875975</v>
+        <v>24.78887505295515</v>
       </c>
       <c r="F6" t="n">
-        <v>26.08018929570513</v>
+        <v>26.52001323984877</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>22.46</v>
+        <v>22.88</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>22.64</v>
+        <v>23.07</v>
       </c>
     </row>
     <row r="4">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>22.7</v>
+        <v>23.14</v>
       </c>
     </row>
   </sheetData>
